--- a/evalpicker/data/evaluation_approaches.xlsx
+++ b/evalpicker/data/evaluation_approaches.xlsx
@@ -3818,7 +3818,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Most of the field is wrong for you.</t>
+          <t>Not every evaluation fits every program.</t>
         </is>
       </c>
     </row>

--- a/evalpicker/data/evaluation_approaches.xlsx
+++ b/evalpicker/data/evaluation_approaches.xlsx
@@ -3998,7 +3998,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Click any card for the full picture.</t>
+          <t>Tap or click any card for the full picture.</t>
         </is>
       </c>
     </row>
